--- a/product_selector_out/STM32L4x1.xlsx
+++ b/product_selector_out/STM32L4x1.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX24" s="4" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AW25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AW27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX28" s="4" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="AW29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX29" s="4" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AW30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX30" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="AW31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX31" s="4" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AW32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX32" s="4" t="inlineStr">
@@ -8703,9 +8703,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="8" t="inlineStr">
@@ -9030,9 +9030,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="8" t="inlineStr">
@@ -9357,9 +9357,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="8" t="inlineStr">
@@ -9684,9 +9684,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="8" t="inlineStr">
@@ -10011,9 +10011,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="8" t="inlineStr">
@@ -10338,9 +10338,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="8" t="inlineStr">
@@ -10665,9 +10665,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="8" t="inlineStr">
@@ -10992,9 +10992,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="8" t="inlineStr">
@@ -11319,9 +11319,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="8" t="inlineStr">
@@ -11646,9 +11646,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="8" t="inlineStr">
@@ -11973,9 +11973,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="8" t="inlineStr">
@@ -12300,9 +12300,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="8" t="inlineStr">
@@ -12627,9 +12627,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="8" t="inlineStr">
@@ -12954,9 +12954,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="8" t="inlineStr">
@@ -13281,9 +13281,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="8" t="inlineStr">
@@ -13608,9 +13608,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="8" t="inlineStr">
@@ -13935,9 +13935,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="8" t="inlineStr">
@@ -14262,9 +14262,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="8" t="inlineStr">
@@ -14589,9 +14589,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="8" t="inlineStr">
@@ -14916,9 +14916,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="8" t="inlineStr">
@@ -15243,9 +15243,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="8" t="inlineStr">
@@ -15344,7 +15344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15481,19 +15481,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15547,19 +15547,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15569,19 +15569,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15613,7 +15613,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15657,19 +15657,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15679,19 +15679,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -15701,14 +15701,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15723,14 +15723,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15752,7 +15752,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15774,12 +15774,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15789,19 +15789,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15811,19 +15811,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15833,19 +15833,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15855,19 +15855,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15877,14 +15877,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15899,14 +15899,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15921,14 +15921,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15972,7 +15972,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -15994,12 +15994,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16009,19 +16009,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16031,19 +16031,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16053,19 +16053,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16075,19 +16075,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16097,14 +16097,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16119,19 +16119,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16141,19 +16141,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16163,19 +16163,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -16185,19 +16185,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -16207,19 +16207,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -16229,14 +16229,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16251,14 +16251,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -16273,14 +16273,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -16295,19 +16295,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -16317,19 +16317,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -16339,19 +16339,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -16361,19 +16361,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -16383,19 +16383,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16405,14 +16405,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -16427,19 +16427,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16449,19 +16449,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16471,19 +16471,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16493,19 +16493,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16515,19 +16515,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16537,14 +16537,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -16559,14 +16559,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -16581,14 +16581,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16603,19 +16603,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16625,19 +16625,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16647,19 +16647,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16669,19 +16669,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16691,19 +16691,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16713,19 +16713,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16735,19 +16735,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16757,19 +16757,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16779,19 +16779,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16801,19 +16801,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -16823,19 +16823,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -16845,19 +16845,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16867,19 +16867,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16889,19 +16889,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16911,19 +16911,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -16933,14 +16933,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -16962,7 +16962,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -16977,14 +16977,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -16999,27 +16999,489 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L471ZE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L431CB</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L431KC</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L471ZG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L431KB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>STM32L431VC</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32L431VC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x1.xlsx
+++ b/product_selector_out/STM32L4x1.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -8548,29 +8548,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr">
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -8593,9 +8593,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -8653,9 +8653,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -8890,14 +8890,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -8920,9 +8920,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -8980,9 +8980,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -9202,29 +9202,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -9247,9 +9247,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -9307,9 +9307,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -9544,14 +9544,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -9574,9 +9574,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -9634,9 +9634,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -9871,14 +9871,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -9901,9 +9901,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -9961,9 +9961,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -10183,29 +10183,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -10228,9 +10228,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -10288,9 +10288,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -10510,29 +10510,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -10555,9 +10555,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -10615,9 +10615,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -10852,14 +10852,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -10882,9 +10882,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">
@@ -10942,9 +10942,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -11179,14 +11179,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
@@ -11209,9 +11209,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="6" t="inlineStr">
@@ -11491,29 +11491,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr">
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
@@ -11536,9 +11536,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="6" t="inlineStr">
@@ -11596,9 +11596,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -11833,14 +11833,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
@@ -11863,9 +11863,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="6" t="inlineStr">
@@ -11923,9 +11923,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -12160,14 +12160,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
@@ -12190,9 +12190,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="6" t="inlineStr">
@@ -12487,14 +12487,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
@@ -12517,9 +12517,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="6" t="inlineStr">
@@ -12799,29 +12799,29 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="7" t="inlineStr">
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
@@ -12844,9 +12844,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="6" t="inlineStr">
@@ -12904,9 +12904,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -13141,14 +13141,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
@@ -13171,9 +13171,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB26" s="6" t="inlineStr">
@@ -13231,9 +13231,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -13468,14 +13468,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
@@ -13498,9 +13498,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="6" t="inlineStr">
@@ -13558,9 +13558,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -13795,14 +13795,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
@@ -13825,9 +13825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB28" s="6" t="inlineStr">
@@ -14122,14 +14122,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
@@ -14152,9 +14152,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB29" s="6" t="inlineStr">
@@ -14449,14 +14449,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
@@ -14479,9 +14479,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="6" t="inlineStr">
@@ -14539,9 +14539,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -14776,14 +14776,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
@@ -14806,9 +14806,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="6" t="inlineStr">
@@ -15103,14 +15103,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
@@ -15133,9 +15133,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB32" s="6" t="inlineStr">
@@ -15344,7 +15344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15459,19 +15459,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15481,19 +15481,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15547,19 +15547,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15569,19 +15569,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15613,7 +15613,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15635,19 +15635,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15657,14 +15657,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15679,14 +15679,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15708,7 +15708,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15723,14 +15723,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15752,7 +15752,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -15796,7 +15796,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -15818,7 +15818,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -15833,14 +15833,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15855,14 +15855,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15884,7 +15884,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15899,14 +15899,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15921,19 +15921,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15943,19 +15943,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15965,19 +15965,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15987,19 +15987,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16009,19 +16009,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16031,19 +16031,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16053,19 +16053,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16075,19 +16075,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16097,14 +16097,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16119,14 +16119,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -16141,14 +16141,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16163,14 +16163,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16185,14 +16185,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16207,14 +16207,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16236,7 +16236,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16251,14 +16251,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -16273,14 +16273,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -16295,14 +16295,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -16317,14 +16317,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -16346,7 +16346,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -16361,19 +16361,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -16383,19 +16383,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16405,19 +16405,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16427,19 +16427,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16449,19 +16449,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16471,19 +16471,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16493,19 +16493,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16515,19 +16515,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16537,19 +16537,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16559,19 +16559,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16581,19 +16581,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16603,19 +16603,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16625,19 +16625,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16647,19 +16647,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16669,19 +16669,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16691,19 +16691,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16713,19 +16713,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16735,19 +16735,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16757,19 +16757,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16779,19 +16779,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16801,14 +16801,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16823,14 +16823,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16845,14 +16845,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16867,14 +16867,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16889,14 +16889,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16911,14 +16911,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -16933,14 +16933,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -16962,7 +16962,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -16984,7 +16984,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17006,7 +17006,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17028,7 +17028,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17050,7 +17050,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17065,14 +17065,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -17116,7 +17116,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -17138,7 +17138,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -17153,14 +17153,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -17182,7 +17182,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -17204,7 +17204,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -17218,270 +17218,6 @@
         </is>
       </c>
       <c r="D85" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32L471ZG</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32L471ZG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32L471ZG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32L471ZG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32L431KB</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32L431KB</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32L431KB</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32L431KB</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32L431VC</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x1.xlsx
+++ b/product_selector_out/STM32L4x1.xlsx
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AM20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN20" s="4" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AM23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN23" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AM24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN24" s="4" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AM28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN28" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AM29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN29" s="4" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN31" s="4" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AM32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN32" s="4" t="inlineStr">
@@ -8653,9 +8653,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -8980,9 +8980,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -9307,9 +9307,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -9634,9 +9634,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -9961,9 +9961,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -10288,9 +10288,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -10615,9 +10615,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -10942,9 +10942,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -11269,9 +11269,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -11596,9 +11596,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -11923,9 +11923,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -12250,9 +12250,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -12577,9 +12577,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -12904,9 +12904,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -13231,9 +13231,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -13558,9 +13558,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -13885,9 +13885,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -14212,9 +14212,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM29" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN29" s="6" t="inlineStr">
@@ -14539,9 +14539,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -14866,9 +14866,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM31" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -15193,9 +15193,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM32" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x1.xlsx
+++ b/product_selector_out/STM32L4x1.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.64453125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -7860,12 +7967,17 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7886,16 +7998,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7908,6 +8018,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -7927,7 +8038,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -7965,7 +8078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8033,6 +8146,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8366,6 +8480,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8461,6 +8580,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8783,7 +8903,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9110,7 +9235,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9437,7 +9567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9764,7 +9899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10091,7 +10231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10418,7 +10563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10745,7 +10895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11072,7 +11227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11399,7 +11559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11726,7 +11891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12053,7 +12223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12380,7 +12555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12707,7 +12887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13034,7 +13219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13361,7 +13551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13688,7 +13883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14015,7 +14215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14342,7 +14547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14669,7 +14879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14996,7 +15211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15323,7 +15543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15331,8 +15556,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
